--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -539,8 +539,6 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>04/08/2026 16:07:02</t>
@@ -588,16 +586,90 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>04/08/2026 16:07:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>/home/sannyer-carvalho/Documentos/Projects/projeto_fani/empresa_portal_fake/HyperAutomation/resources/Documentos_Aprovados/solicitacao_completa_ana_silva.pdf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nome, CPF, E-mail, Telefone, Nascimento, Endereco</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PDF invalido ou nao pode ser lido: Stream has ended unexpectedly</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18/08/2026 10:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>/home/sannyer-carvalho/Documentos/Projects/projeto_fani/empresa_portal_fake/HyperAutomation/resources/Documentos_Aprovados/solicitacao_completa_ana_silva.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ana Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>111.222.333-44</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ana.silva@exemplo.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(92) 98888-1111</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15/05/1992</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rua das Palmeiras, 120 - Manaus/AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>18/08/2026 10:14:42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -539,8 +539,6 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>04/08/2026 16:07:02</t>
@@ -588,16 +586,63 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>04/08/2026 16:07:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documento_do_Cliente_02033414221.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fani</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>020.334.142-21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fani.souza19@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(92) 99503-7524</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rua Rio Purus, 915 - Bairro Taruma-Acu - Manaus/AM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18/08/2026 10:04:54</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$Q$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -436,9 +436,15 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,6 +503,36 @@
           <t>Atualizado em</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Status Cadastro</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo Erro Cadastro</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Data Cadastro</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Status SAC</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Protocolo SAC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Data Envio SAC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,6 +580,31 @@
           <t>04/08/2026 16:07:02</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:18</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CONFIRMACAO_ENVIADA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>#SAC-2026-3135</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:42</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +652,31 @@
           <t>04/08/2026 16:07:02</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:20</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CONFIRMACAO_ENVIADA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>#SAC-2026-8809</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:42</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,16 +719,116 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18/08/2026 10:04:54</t>
+          <t>23/08/2026 22:11:13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ERRO_CADASTRO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Erro no preenchimento/validação do formulário: Erro na validação do formulário</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:24</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>#SAC-2026-8816</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>resources/Documentos_Aprovados/documento_teste_lucas.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lucas Henrique Lima</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>111.444.777-35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lucas.lima@exemplo.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(92) 99123-4567</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10/04/1996</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rua das Palmeiras, 500 - Manaus/AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23/08/2026 21:57:18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:26</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>CONFIRMACAO_ENVIADA</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>#SAC-2026-5467</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>23/08/2026 22:11:42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:Q5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -582,27 +582,32 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:18</t>
+          <t>24/08/2026 11:01:56</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>#SAC-2026-3135</t>
+          <t>#SAC-2026-1653</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:42</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
@@ -654,39 +659,44 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:20</t>
+          <t>24/08/2026 11:01:57</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>#SAC-2026-8809</t>
+          <t>#SAC-2026-4292</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:42</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documento_do_Cliente_02033414221.pdf</t>
+          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\ERP_Portal_Fake\Documentos_OK\Documento_do_Cliente_02033414221.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fani</t>
+          <t>Fani Batista</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,22 +731,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:13</t>
+          <t>24/08/2026 11:01:01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ERRO_CADASTRO</t>
+          <t>DUPLICADO</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Erro no preenchimento/validação do formulário: Erro na validação do formulário</t>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:24</t>
+          <t>24/08/2026 11:01:58</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -746,12 +756,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>#SAC-2026-8816</t>
+          <t>#SAC-2026-2122</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:42</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
@@ -803,27 +813,32 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:26</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>#SAC-2026-5467</t>
+          <t>#SAC-2026-6072</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:42</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$Q$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$Q$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +27,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -57,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,8 +436,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -448,87 +459,87 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Arquivo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>CPF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Telefone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Nascimento</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Endereco</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Campos ausentes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Erro</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Atualizado em</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Status Cadastro</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Motivo Erro Cadastro</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Data Cadastro</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Status SAC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Protocolo SAC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Data Envio SAC</t>
         </is>
@@ -537,313 +548,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\Turma02\Documents\GitHub\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\documento_ficticio_1.pdf</t>
+          <t>C:\Users\Turma02\Documents\HYPERAUTOMATION\PROJETO FINAL\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documentos_do_cliente_03536054250.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>João Pedro Almeida</t>
+          <t>Sannyer Nery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>123.456.789-09</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>joao.almeida.teste@example.com</t>
+          <t>035.360.542-50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(11) 98765-4321</t>
+          <t>(92) 99982-7524</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15/03/1995</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rua das Acácias, 120 - Centro, São Paulo/SP - CEP 01000-000</t>
+          <t>Rua Rio Purus, 915 - Bairro Taruma-Acu - Manaus/AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Campos obrigatorios nao encontrados: E-mail</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>04/08/2026 16:07:02</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:56</t>
+          <t>24/08/2026 17:41:27</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>#SAC-2026-1653</t>
+          <t>#SAC-2026-7378</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C:\Users\Turma02\Documents\GitHub\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\documento_ficticio_2.pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mariana Costa Ribeiro</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>987.654.321-00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>mariana.ribeiro.teste@example.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(21) 99876-1234</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22/08/1992</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Av. Atlântica, 850 - Copacabana, Rio de Janeiro/RJ - CEP 22000-000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>04/08/2026 16:07:02</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:57</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>#SAC-2026-4292</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\ERP_Portal_Fake\Documentos_OK\Documento_do_Cliente_02033414221.pdf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fani Batista</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>020.334.142-21</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>fani.souza19@gmail.com</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(92) 99503-7524</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rua Rio Purus, 915 - Bairro Taruma-Acu - Manaus/AM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:58</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>#SAC-2026-2122</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>resources/Documentos_Aprovados/documento_teste_lucas.pdf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lucas Henrique Lima</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>111.444.777-35</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>lucas.lima@exemplo.com</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(92) 99123-4567</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10/04/1996</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rua das Palmeiras, 500 - Manaus/AM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>23/08/2026 21:57:18</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>#SAC-2026-6072</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 17:41:52</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q5"/>
+  <autoFilter ref="A1:Q2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -582,32 +582,27 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:56</t>
+          <t>24/08/2026 11:11:19</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>#SAC-2026-1653</t>
+          <t>#SAC-2026-7466</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
@@ -659,32 +654,27 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:57</t>
+          <t>24/08/2026 11:11:21</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>#SAC-2026-4292</t>
+          <t>#SAC-2026-3585</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
@@ -736,32 +726,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:58</t>
+          <t>24/08/2026 11:11:22</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>#SAC-2026-2122</t>
+          <t>#SAC-2026-2116</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
@@ -813,32 +798,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:24</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>#SAC-2026-6072</t>
+          <t>#SAC-2026-5161</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\Turma02\Documents\HYPERAUTOMATION\PROJETO FINAL\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documentos_do_cliente_03536054250.pdf</t>
+          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documentos_do_cliente_03536054250.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -561,6 +561,7 @@
           <t>035.360.542-50</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>(92) 99982-7524</t>
@@ -593,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24/08/2026 17:41:27</t>
+          <t>24/08/2026 21:34:48</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="596" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
@@ -437,7 +437,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -548,28 +548,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documentos_do_cliente_03536054250.pdf</t>
+          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documento_do_Cliente_02033414221.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sannyer Nery</t>
+          <t>Fani Batista</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>035.360.542-50</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>020.334.142-21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fani.souza19@gmail.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(92) 99982-7524</t>
+          <t>(92) 99503-7524</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -579,22 +583,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Campos obrigatorios nao encontrados: E-mail</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24/08/2026 21:34:48</t>
+          <t>24/08/2026 22:15:42</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>24/08/2026 22:16:21</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -604,12 +608,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>#SAC-2026-7378</t>
+          <t>#SAC-2026-8414</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>24/08/2026 17:41:52</t>
+          <t>24/08/2026 22:16:26</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/planilha_mestra.xlsx
+++ b/HyperAutomation/resources/planilha_mestra.xlsx
@@ -1,45 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D03BFE3-36EB-4982-991F-306F2BAC6D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="596" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados extraidos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados extraidos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados extraidos'!$A$1:$Q$2</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Arquivo</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>CPF</t>
+  </si>
+  <si>
+    <t>E-mail</t>
+  </si>
+  <si>
+    <t>Telefone</t>
+  </si>
+  <si>
+    <t>Nascimento</t>
+  </si>
+  <si>
+    <t>Endereco</t>
+  </si>
+  <si>
+    <t>Sucesso</t>
+  </si>
+  <si>
+    <t>Campos ausentes</t>
+  </si>
+  <si>
+    <t>Erro</t>
+  </si>
+  <si>
+    <t>Atualizado em</t>
+  </si>
+  <si>
+    <t>Status Cadastro</t>
+  </si>
+  <si>
+    <t>Motivo Erro Cadastro</t>
+  </si>
+  <si>
+    <t>Data Cadastro</t>
+  </si>
+  <si>
+    <t>Status SAC</t>
+  </si>
+  <si>
+    <t>Protocolo SAC</t>
+  </si>
+  <si>
+    <t>Data Envio SAC</t>
+  </si>
+  <si>
+    <t>24/08/2026 22:15:42</t>
+  </si>
+  <si>
+    <t>SUCESSO</t>
+  </si>
+  <si>
+    <t>24/08/2026 22:16:21</t>
+  </si>
+  <si>
+    <t>CONFIRMACAO_ENVIADA</t>
+  </si>
+  <si>
+    <t>#SAC-2026-8414</t>
+  </si>
+  <si>
+    <t>24/08/2026 22:16:26</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,11 +123,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,83 +138,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -431,194 +442,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="35" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Arquivo</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>CPF</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Telefone</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Nascimento</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Endereco</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Sucesso</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Campos ausentes</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Erro</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Atualizado em</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Status Cadastro</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Motivo Erro Cadastro</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Data Cadastro</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Status SAC</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Protocolo SAC</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Data Envio SAC</t>
-        </is>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\Documentos_Aprovados\Documento_do_Cliente_02033414221.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fani Batista</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>020.334.142-21</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>fani.souza19@gmail.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(92) 99503-7524</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Rua Rio Purus, 915 - Bairro Taruma-Acu - Manaus/AM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>24/08/2026 22:15:42</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>24/08/2026 22:16:21</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>CONFIRMACAO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>#SAC-2026-8414</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>24/08/2026 22:16:26</t>
-        </is>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:Q2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>